--- a/data/Questions.xlsx
+++ b/data/Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\I-SENSEI.AI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A004D8-6E49-4C3E-84BA-F757BCE9A90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC5C0EC-9CA8-45F0-8E84-273E6FD7F750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8553F202-95DC-4E5C-A378-277AC31D253B}"/>
   </bookViews>

--- a/data/Questions.xlsx
+++ b/data/Questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\I-SENSEI.AI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC5C0EC-9CA8-45F0-8E84-273E6FD7F750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995C244A-6965-4C3D-955A-C08B7DE48BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8553F202-95DC-4E5C-A378-277AC31D253B}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8553F202-95DC-4E5C-A378-277AC31D253B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Questions</t>
   </si>
@@ -55,6 +55,96 @@
   </si>
   <si>
     <t>Tell us about a time that you had to adapt to a difficult situation.</t>
+  </si>
+  <si>
+    <t>What do you do when priorities change quickly? Give one example of when this happened.</t>
+  </si>
+  <si>
+    <t>Describe a project or idea that was implemented primarily because of your efforts. What was your role? What was the outcome?</t>
+  </si>
+  <si>
+    <t>Describe a time when you made a suggestion to improve the work in your organization.</t>
+  </si>
+  <si>
+    <t>Give an example of an important goal that you set in the past. Tell about your success in reaching it.</t>
+  </si>
+  <si>
+    <t>Give two examples of things you've done in previous jobs t hat demonstrate your willingness to work hard.</t>
+  </si>
+  <si>
+    <t>How many hours a day do you put into your work? What were your study patterns at school?</t>
+  </si>
+  <si>
+    <t>Tell us about a time when you had to go above and beyond the call of duty in order to get a job done.</t>
+  </si>
+  <si>
+    <t>Tell us about a time when a job had to be completed and you were able to focus your attention and efforts to get it done.</t>
+  </si>
+  <si>
+    <t>Tell us about a time when you were particularly effective on prioritizing tasks and completing a project on schedule.</t>
+  </si>
+  <si>
+    <t>Tell us about the last time that you undertook a project that demanded a lot of initiative.</t>
+  </si>
+  <si>
+    <t>Tell us how you keep your job knowledge current with the on going changes in the industry.</t>
+  </si>
+  <si>
+    <t>There are times when we work without close supervision or support to get the job done. Tell us about a time when you found yourself in such a situation and how things turned out.</t>
+  </si>
+  <si>
+    <t>What impact did you have in your last job?</t>
+  </si>
+  <si>
+    <t>What is the most competitive work situation you have experienced? How did you handle it? What was the result?</t>
+  </si>
+  <si>
+    <t>What is the riskiest decision you have made? What was the situation? What happened?</t>
+  </si>
+  <si>
+    <t>What kinds of challenges did you face on your last job? Give an example of how you handled them.</t>
+  </si>
+  <si>
+    <t>What projects have you started on your own recently? What prompted you to get started?</t>
+  </si>
+  <si>
+    <t>What sorts of things have you done to become better qualified for your career?</t>
+  </si>
+  <si>
+    <t>What was the best idea that you came up with in your career? How did you apply it?</t>
+  </si>
+  <si>
+    <t>When you disagree with your manager, what do you do? Give an example.</t>
+  </si>
+  <si>
+    <t>When you have a lot of work to do, how do you get it all done? Give an example?</t>
+  </si>
+  <si>
+    <t>Give a specific example of a time when you had to address an angry customer. What was the problem and what was the outcome? How would you asses your role in diffusing the situation?</t>
+  </si>
+  <si>
+    <t>It is very important to build good relationships at work but sometimes it doesn't always work. If you can, tell about a time when you were not able to build a successful relationship with a difficult person.</t>
+  </si>
+  <si>
+    <t>Tell us about a time when you built rapport quickly with someone under difficult conditions.</t>
+  </si>
+  <si>
+    <t>Tell us about a politically complex work situation in which you worked.</t>
+  </si>
+  <si>
+    <t>Have you ever worked in a situation where the rules and guidelines were not clear? Tell me about it. How did you feel about it? How did you react?</t>
+  </si>
+  <si>
+    <t>Tell us me about a time when you demonstrated too much initiative?</t>
+  </si>
+  <si>
+    <t>Describe a situation when you were able to strengthen a relationship by communicating effectively. What made your communication effective?</t>
+  </si>
+  <si>
+    <t>Describe a situation where you felt you had not communicated well. How did you correct the situation?</t>
+  </si>
+  <si>
+    <t>Discuss an important decision you have made regarding a task or project at work. What factors influenced your decision?</t>
   </si>
 </sst>
 </file>
@@ -406,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67902FFD-C632-4E34-8BD3-FE602B16F8A6}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="181.33203125" customWidth="1"/>
@@ -462,6 +552,156 @@
         <v>9</v>
       </c>
     </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
